--- a/documentação/Testes/Caso de Teste/UC25 - HISTORICO DE CONSULTAS.xlsx
+++ b/documentação/Testes/Caso de Teste/UC25 - HISTORICO DE CONSULTAS.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Casos de Teste" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Casos de Teste" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
   <si>
     <t xml:space="preserve">Caso de Teste</t>
   </si>
@@ -194,9 +194,6 @@
   </si>
   <si>
     <t xml:space="preserve">Nova consulta aparece na tabela sem recarregar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">não dá para agendar a consulta</t>
   </si>
   <si>
     <t xml:space="preserve">CT-12</t>
@@ -420,13 +417,119 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="32.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="32.2421875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.04"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="32.22"/>
@@ -678,24 +781,21 @@
         <v>27</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>36</v>
